--- a/huion_k20/huion_layout.xls.xlsx
+++ b/huion_k20/huion_layout.xls.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a02d7747fd16c87/Documents/GitHub/WaterPoloScoreBoard/huion_k20/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amdcloud-my.sharepoint.com/personal/tmakepea_amd_com/Documents/Documents/waterpolo/WaterPoloScoreBoard/huion_k20/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{59AB3520-E6C2-400C-B99F-2F49CA16BCBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EB04BE3-A33B-43CC-BBF0-1CDCED3EC573}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{59AB3520-E6C2-400C-B99F-2F49CA16BCBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C8D0D0E-C984-45BD-BEA8-733BA64FD151}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{7913F6BC-D14F-4780-AD20-51F26E16B15C}"/>
+    <workbookView xWindow="43260" yWindow="1580" windowWidth="28800" windowHeight="15450" xr2:uid="{7913F6BC-D14F-4780-AD20-51F26E16B15C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,33 +36,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>10 (Y)</t>
-  </si>
-  <si>
-    <t>11 (U)</t>
-  </si>
-  <si>
-    <t>12 (I)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Major 
 13 (C)</t>
   </si>
   <si>
-    <t>Goal (V)</t>
-  </si>
-  <si>
     <t>Penalty (B)</t>
-  </si>
-  <si>
-    <t>Home Card 
-6 ("F")</t>
-  </si>
-  <si>
-    <t>Away Card 
-7  ("G")</t>
   </si>
   <si>
     <t>Home TimeOut
@@ -80,15 +60,49 @@
   </si>
   <si>
     <t>Start/Stop (N)</t>
+  </si>
+  <si>
+    <t>Card 
+6 ("F")</t>
+  </si>
+  <si>
+    <t>Pause Poss
+9 (H)</t>
+  </si>
+  <si>
+    <t>Possession
+10 (Y)</t>
+  </si>
+  <si>
+    <t>Shot
+11 (U)</t>
+  </si>
+  <si>
+    <t>Goal 
+14 (V)</t>
+  </si>
+  <si>
+    <t>Corner
+12 (J)</t>
+  </si>
+  <si>
+    <t>Buzzer 
+7 ("G")</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -179,34 +193,34 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
   </cellXfs>
@@ -544,75 +558,75 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8864E4D2-07DF-4830-9804-A61C703E51BD}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="9.59765625" customWidth="1"/>
+    <col min="1" max="4" width="9.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="57.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1">
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D1" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="57.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D2" s="4">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+    <row r="3" spans="1:5" ht="57.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="57.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="D4" s="9" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E4" s="6"/>
     </row>
-    <row r="5" spans="1:5" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="57.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="6"/>
